--- a/lab-standards/BACI-lab-standard.xlsx
+++ b/lab-standards/BACI-lab-standard.xlsx
@@ -561,6 +561,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -576,6 +580,10 @@
 Classroom cum workshop – 1500 sft (140 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -645,7 +653,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -667,7 +677,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -689,7 +701,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -711,7 +725,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -733,7 +749,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -755,7 +773,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -777,7 +797,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -799,7 +821,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -821,7 +845,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -843,7 +869,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -865,7 +893,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -1011,6 +1041,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1025,6 +1059,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1094,7 +1132,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1116,7 +1156,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1138,7 +1180,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1160,7 +1204,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -1182,7 +1228,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1204,7 +1252,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1226,7 +1276,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1248,7 +1300,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1270,7 +1324,9 @@
       <c r="C24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1292,7 +1348,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1314,7 +1372,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -1336,7 +1396,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -1358,7 +1420,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -1380,7 +1444,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -1402,7 +1468,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1424,7 +1492,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -1446,7 +1516,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1468,7 +1540,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1490,7 +1564,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -1512,7 +1588,9 @@
       <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1534,7 +1612,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -1556,7 +1636,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1578,7 +1660,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -1724,6 +1808,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1738,6 +1826,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1807,7 +1899,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1829,7 +1923,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1851,7 +1947,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1873,7 +1971,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -1895,7 +1995,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -1917,7 +2019,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1939,7 +2043,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1961,7 +2067,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1983,7 +2091,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2005,7 +2115,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2027,7 +2139,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -2049,7 +2163,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -2071,7 +2187,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -2093,7 +2211,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -2115,7 +2235,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -2137,7 +2259,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -2159,7 +2283,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -2181,7 +2307,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -2203,7 +2331,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>9</v>
       </c>
@@ -2225,7 +2355,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -2247,7 +2379,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -2269,7 +2403,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -2291,7 +2427,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -2437,6 +2575,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2452,6 +2594,10 @@
 Classroom cum workshop – 1000 sft (93 sqm) Space for Plumbing booth not included</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2521,7 +2667,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2543,7 +2691,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2565,7 +2715,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -2587,7 +2739,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -2609,7 +2763,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2755,6 +2911,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2770,6 +2930,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2839,7 +3003,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2861,7 +3027,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2883,7 +3051,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2905,7 +3075,9 @@
       <c r="C19" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2927,7 +3099,9 @@
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -2949,7 +3123,9 @@
       <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -2971,7 +3147,9 @@
       <c r="C22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2993,7 +3171,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -3015,7 +3195,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3037,7 +3219,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -3059,7 +3243,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3081,7 +3267,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -3103,7 +3291,9 @@
       <c r="C28" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -3249,6 +3439,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3263,6 +3457,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3332,7 +3530,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -3354,7 +3554,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -3376,7 +3578,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -3398,7 +3602,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -3420,7 +3626,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3442,7 +3650,9 @@
       <c r="C21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -3464,7 +3674,9 @@
       <c r="C22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -3486,7 +3698,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -3508,7 +3722,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3530,7 +3746,9 @@
       <c r="C25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -3552,7 +3770,9 @@
       <c r="C26" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3574,7 +3794,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -3596,7 +3818,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>

--- a/lab-standards/BACI-lab-standard.xlsx
+++ b/lab-standards/BACI-lab-standard.xlsx
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
